--- a/data/trans_dic/P3A$otraSIcobra-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraSIcobra-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y cobra por ello, se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y cobra por ello se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,69</t>
+          <t>2,22; 4,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,25</t>
+          <t>2,29; 4,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,06</t>
+          <t>2,57; 4,2</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,99</t>
+          <t>0,76; 3,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,74</t>
+          <t>2,07; 3,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,89</t>
+          <t>1,42; 2,94</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,43</t>
+          <t>1,54; 4,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,97</t>
+          <t>1,15; 3,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,57</t>
+          <t>1,7; 3,53</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,4</t>
+          <t>2,78; 5,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,55</t>
+          <t>3,36; 5,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 5,01</t>
+          <t>3,42; 5,1</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,43</t>
+          <t>2,11; 3,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 3,84</t>
+          <t>2,68; 3,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,61; 3,5</t>
+          <t>2,6; 3,53</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y cobra por ello, se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y cobra por ello se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14019; 29750</t>
+          <t>14090; 29883</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17050; 30791</t>
+          <t>16604; 31261</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34487; 55266</t>
+          <t>34936; 57067</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9649; 35689</t>
+          <t>9046; 35732</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19871; 35865</t>
+          <t>19848; 35752</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31243; 62173</t>
+          <t>30599; 63357</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11498; 31187</t>
+          <t>10887; 29511</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12801; 37098</t>
+          <t>10688; 36396</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27850; 58543</t>
+          <t>27824; 57793</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26241; 50014</t>
+          <t>25793; 49549</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36635; 60748</t>
+          <t>36784; 62019</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68868; 101262</t>
+          <t>69106; 103050</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>71217; 118540</t>
+          <t>72969; 117979</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>101413; 142650</t>
+          <t>99331; 143985</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>187029; 251003</t>
+          <t>186252; 253087</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$otraSIcobra-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraSIcobra-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,71</t>
+          <t>2,18; 4,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,31</t>
+          <t>2,73; 4,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,2</t>
+          <t>2,72; 4,3</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,0</t>
+          <t>1,34; 3,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,73</t>
+          <t>2,11; 3,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,94</t>
+          <t>1,95; 3,26</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,19</t>
+          <t>1,56; 4,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,9</t>
+          <t>2,72; 4,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,53</t>
+          <t>2,48; 4,05</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,35</t>
+          <t>2,7; 5,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 5,67</t>
+          <t>3,7; 5,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 5,1</t>
+          <t>3,49; 5,13</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,41</t>
+          <t>2,43; 3,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,68; 3,88</t>
+          <t>3,16; 4,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 3,53</t>
+          <t>2,96; 3,69</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21042</t>
+          <t>22425</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23445</t>
+          <t>26279</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44486</t>
+          <t>48704</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14090; 29883</t>
+          <t>15079; 32063</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16604; 31261</t>
+          <t>20007; 35047</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34936; 57067</t>
+          <t>38787; 61241</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>19973</t>
+          <t>23240</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>26954</t>
+          <t>30166</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46927</t>
+          <t>53407</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9046; 35732</t>
+          <t>14038; 36225</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19848; 35752</t>
+          <t>22617; 39606</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30599; 63357</t>
+          <t>41330; 69171</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18225</t>
+          <t>21397</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25085</t>
+          <t>29368</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43310</t>
+          <t>50765</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10887; 29511</t>
+          <t>12539; 33125</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10688; 36396</t>
+          <t>22067; 39211</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27824; 57793</t>
+          <t>40005; 65449</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>35971</t>
+          <t>36864</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>48401</t>
+          <t>52059</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84372</t>
+          <t>88923</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25793; 49549</t>
+          <t>26745; 50696</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36784; 62019</t>
+          <t>41404; 65330</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69106; 103050</t>
+          <t>73564; 108028</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>95211</t>
+          <t>103927</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>123885</t>
+          <t>137872</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>219096</t>
+          <t>241799</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>72969; 117979</t>
+          <t>85939; 127884</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>99331; 143985</t>
+          <t>118070; 156332</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>186252; 253087</t>
+          <t>215168; 268184</t>
         </is>
       </c>
     </row>
